--- a/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original_1.xlsx
+++ b/dev_test/Diversification/Self Created Dataset/Manual Created Diversified Dataset/Disturbed Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\table-diversification\dev_test\Diversification\Self Created Dataset\Manual Created Diversified Dataset\Disturbed Diversifications\Retail_Sales_Orders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E610F73-F9AA-4A60-A7F8-0DECD038D3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A76F6D-E524-44DE-9A0A-8229BD97E68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -706,14 +706,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -770,6 +770,12 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
       <c r="G2" t="s">
         <v>20</v>
       </c>
@@ -795,7 +801,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -809,10 +815,10 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -839,7 +845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -853,10 +859,10 @@
         <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
         <v>37</v>
@@ -883,7 +889,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -927,95 +933,95 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
         <v>20</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>6</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>15</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>90</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>85.5</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>21</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>19</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>20</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>15</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0</v>
-      </c>
-      <c r="K7">
-        <v>75</v>
       </c>
       <c r="L7">
         <v>75</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7">
+        <v>75</v>
+      </c>
+      <c r="N7" t="s">
         <v>21</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1029,10 +1035,10 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1059,7 +1065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1073,10 +1079,10 @@
         <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
@@ -1103,7 +1109,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1117,10 +1123,10 @@
         <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
         <v>37</v>
@@ -1147,7 +1153,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -1161,10 +1167,10 @@
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
         <v>56</v>
@@ -1191,7 +1197,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -1235,7 +1241,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -1249,10 +1255,10 @@
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
         <v>56</v>
@@ -1279,7 +1285,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1293,10 +1299,10 @@
         <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
@@ -1323,7 +1329,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -1337,10 +1343,10 @@
         <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
         <v>37</v>
@@ -1367,7 +1373,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>77</v>
       </c>
@@ -1381,10 +1387,10 @@
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
@@ -1411,7 +1417,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -1425,10 +1431,10 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
         <v>56</v>
@@ -1455,7 +1461,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -1509,41 +1515,41 @@
       <c r="C19" t="s">
         <v>88</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>46</v>
       </c>
-      <c r="E19" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
         <v>20</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>6</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>15</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.1</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>90</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>81</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>29</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -1553,41 +1559,41 @@
       <c r="C20" t="s">
         <v>91</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>46</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>18</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>19</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>20</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>1</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>15</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.05</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>15</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>14.25</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>29</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -1601,10 +1607,10 @@
         <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
         <v>56</v>
@@ -1631,7 +1637,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -1645,10 +1651,10 @@
         <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>56</v>
@@ -1675,7 +1681,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -1689,10 +1695,10 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1719,7 +1725,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>102</v>
       </c>
@@ -1733,10 +1739,10 @@
         <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
         <v>56</v>
@@ -1763,7 +1769,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>105</v>
       </c>
@@ -1777,10 +1783,10 @@
         <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
         <v>37</v>
@@ -1805,14 +1811,6 @@
       </c>
       <c r="N25" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E26" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
